--- a/users_login.xlsx
+++ b/users_login.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\games\New folder\solve error\school-growth-hub-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15818C6D-3C06-4BCC-8394-4533BAF01319}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0714189D-20B3-4BC1-AFB1-8DD03A455EBE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17490" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17490" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -524,7 +524,7 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
@@ -606,6 +606,8 @@
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{295D0147-7C3E-490E-B939-5218A9B618A9}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{C01CBD9E-451C-4E6C-A333-4DD57018325B}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{9CC6AC2E-92C9-467E-BBC2-5F0CB4C60971}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{13D2CD70-DD52-4216-B483-B19EA6C0B9B3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
